--- a/eastleigh_updated_dash_app/Eastleigh_Masterlist.xlsx
+++ b/eastleigh_updated_dash_app/Eastleigh_Masterlist.xlsx
@@ -975,8 +975,8 @@
         <v>34</v>
       </c>
       <c r="C26" s="2">
-        <f>D19</f>
-        <v>35726647</v>
+        <f>D17</f>
+        <v>35726645</v>
       </c>
       <c r="D26" s="2">
         <v>3.5775692E7</v>
@@ -996,8 +996,8 @@
         <v>35</v>
       </c>
       <c r="C27" s="2">
-        <f>D19</f>
-        <v>35726647</v>
+        <f t="shared" ref="C27:C28" si="4">D17</f>
+        <v>35726645</v>
       </c>
       <c r="D27" s="2">
         <v>3.5779529E7</v>
@@ -1017,7 +1017,7 @@
         <v>36</v>
       </c>
       <c r="C28" s="2">
-        <f>D18</f>
+        <f t="shared" si="4"/>
         <v>35779560</v>
       </c>
       <c r="D28" s="2">
